--- a/CSV/ocean monument.xlsx
+++ b/CSV/ocean monument.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/CSV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C91768-0600-4B4E-AC91-0A0F909A3299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6431C1-2ED0-A44E-9F56-013270FB8521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19120" xr2:uid="{07D44569-79BD-4F9D-B81C-4BABD9EEFACF}"/>
+    <workbookView xWindow="0" yWindow="9560" windowWidth="11480" windowHeight="10060" xr2:uid="{07D44569-79BD-4F9D-B81C-4BABD9EEFACF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,13 +41,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>nummer</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
     <t>Z</t>
+  </si>
+  <si>
+    <t>Ocean Monument</t>
   </si>
 </sst>
 </file>
@@ -421,16 +421,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15958F6C-D0C3-4305-981B-73D19B23D0A4}">
   <dimension ref="A1:C72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
